--- a/ABA_mining/outputs/eval/task3/check-in/llama3.2/contrary_v3/Contrary(P)Body(N).xlsx
+++ b/ABA_mining/outputs/eval/task3/check-in/llama3.2/contrary_v3/Contrary(P)Body(N).xlsx
@@ -17283,16 +17283,16 @@
         <v>65</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3815789473684211</v>
+        <v>0.381579</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3085106382978723</v>
+        <v>0.308511</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3411764705882353</v>
+        <v>0.341177</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.555556</v>
       </c>
     </row>
     <row r="3">
@@ -17342,16 +17342,16 @@
         <v>65</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3815789473684211</v>
+        <v>0.381579</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3085106382978723</v>
+        <v>0.308511</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3411764705882353</v>
+        <v>0.341177</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.555556</v>
       </c>
     </row>
     <row r="4">
@@ -17401,16 +17401,16 @@
         <v>65</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3815789473684211</v>
+        <v>0.381579</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3085106382978723</v>
+        <v>0.308511</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3411764705882353</v>
+        <v>0.341177</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.555556</v>
       </c>
     </row>
   </sheetData>
